--- a/data/obx_xlsx/KOA.OL.xlsx
+++ b/data/obx_xlsx/KOA.OL.xlsx
@@ -11429,14 +11429,29 @@
       <c r="P49" s="15">
         <v>1027.22</v>
       </c>
-      <c r="Q49" s="16"/>
+      <c r="Q49" s="16">
+        <f>SUM(Q51,Q54,Q59,Q62)</f>
+        <v>1166.94</v>
+      </c>
       <c r="R49" s="15">
         <v>1403.8</v>
       </c>
-      <c r="S49" s="16"/>
-      <c r="T49" s="16"/>
-      <c r="U49" s="16"/>
-      <c r="V49" s="16"/>
+      <c r="S49" s="16">
+        <f t="shared" ref="S49:V49" si="1">SUM(S51,S53,S58)</f>
+        <v>1319</v>
+      </c>
+      <c r="T49" s="16">
+        <f t="shared" si="1"/>
+        <v>459</v>
+      </c>
+      <c r="U49" s="16">
+        <f t="shared" si="1"/>
+        <v>416</v>
+      </c>
+      <c r="V49" s="16">
+        <f t="shared" si="1"/>
+        <v>286.4</v>
+      </c>
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
